--- a/data_processed/results_XGB_pkm_car_per_capitaincome.xlsx
+++ b/data_processed/results_XGB_pkm_car_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.7735" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9389" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2104.006103515625</v>
+        <v>1390.046508789062</v>
       </c>
       <c r="D2" t="n">
-        <v>41.82455444335938</v>
+        <v>31.03445434570312</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73.24825286865234</v>
+        <v>519.70068359375</v>
       </c>
       <c r="D3" t="n">
-        <v>1.456067800521851</v>
+        <v>11.60294055938721</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>119.2256011962891</v>
+        <v>110.2164535522461</v>
       </c>
       <c r="D4" t="n">
-        <v>2.370030164718628</v>
+        <v>2.460714340209961</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>874.0157470703125</v>
+        <v>282.2821044921875</v>
       </c>
       <c r="D5" t="n">
-        <v>17.3741512298584</v>
+        <v>6.302286148071289</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>405.5190124511719</v>
+        <v>394.3484802246094</v>
       </c>
       <c r="D6" t="n">
-        <v>8.061123847961426</v>
+        <v>8.804302215576172</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_depstore</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>214.5349884033203</v>
+        <v>81.12472534179688</v>
       </c>
       <c r="D7" t="n">
-        <v>4.264640808105469</v>
+        <v>1.811206698417664</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>229.9730377197266</v>
+        <v>178.1946258544922</v>
       </c>
       <c r="D8" t="n">
-        <v>4.571527004241943</v>
+        <v>3.978408575057983</v>
       </c>
     </row>
     <row r="9">
@@ -563,46 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>cars_per_adult</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>480.8824768066406</v>
+        <v>1523.129272460938</v>
       </c>
       <c r="D9" t="n">
-        <v>9.559238433837891</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dwelling_size</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>101.0251388549805</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.008231639862061</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>cars_per_adult</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>428.1222839355469</v>
-      </c>
-      <c r="D11" t="n">
-        <v>8.510442733764648</v>
+        <v>34.00568389892578</v>
       </c>
     </row>
   </sheetData>
